--- a/SINGLE HADITH CONTENT/missing_input/[V1] MAJAH-(TAWHEED)-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] MAJAH-(TAWHEED)-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C252"/>
+  <dimension ref="A1:C257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4700,6 +4700,91 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا يَعْقُوبُ بْنُ حُمَيْدِ بْنِ كَاسِبٍ، حَدَّثَنَا عَبْدُ الْعَزِيزِ بْنُ مُحَمَّدٍ الدَّرَاوَرْدِيُّ، عَنْ عُبَيْدِ اللَّهِ بْنِ عُمَرَ، عَنْ إِبْرَاهِيمَ بْنِ مُحَمَّدِ بْنِ عَبْدِ اللَّهِ بْنِ جَحْشٍ، عَنْ أَبِيهِ، عَنْ زَيْنَبَ بِنْتِ جَحْشٍ، أَنَّهُ كَانَ لَهَا مِخْضَبٌ مِنْ صُفْرٍ قَالَتْ فَكُنْتُ أُرَجِّلُ رَأْسَ رَسُولِ اللَّهِ ـ صلى الله عليه وسلم ـ فِيهِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>তাঁর পিতলের একটি পাত্র ছিল। তিনি বলেন, আমি তাতে রাসূলুল্লাহ (صلى الله عليه وسلم)-এর চুল আঁচড়াতাম।</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا هِشَامُ بْنُ عَمَّارٍ، حَدَّثَنَا عَبْدُ الْحَمِيدِ بْنُ حَبِيبِ بْنِ أَبِي الْعِشْرِينَ، حَدَّثَنَا الأَوْزَاعِيُّ، عَنْ عَطَاءِ بْنِ أَبِي رَبَاحٍ، قَالَ سَمِعْتُ ابْنَ عَبَّاسٍ، يُخْبِرُ أَنَّ رَجُلاً، أَصَابَهُ جُرْحٌ فِي رَأْسِهِ عَلَى عَهْدِ رَسُولِ اللَّهِ ـ صلى الله عليه وسلم ـ ثُمَّ أَصَابَهُ احْتِلاَمٌ فَأُمِرَ بِالاِغْتِسَالِ فَاغْتَسَلَ فَكُزَّ فَمَاتَ فَبَلَغَ ذَلِكَ النَّبِيَّ ـ صلى الله عليه وسلم ـ فَقَالَ ‏"‏ قَتَلُوهُ قَتَلَهُمُ اللَّهُ أَفَلَمْ يَكُنْ شِفَاءَ الْعِيِّ السُّؤَالُ ‏"‏ ‏.‏ قَالَ عَطَاءٌ وَبَلَغَنَا أَنَّ النَّبِيَّ ـ صلى الله عليه وسلم ـ قَالَ ‏"‏ لَوْ غَسَلَ جَسَدَهُ وَتَرَكَ رَأْسَهُ حَيْثُ أَصَابَهُ الْجِرَاحُ ‏"‏ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>রসূলুল্লাহ (صلى الله عليه وسلم)-এর যমানায় এক ব্যক্তি মাথায় আঘাত পেয়ে আহত হলো, অতঃপর তার স্বপ্নদোষ হলো। তাকে গোসলের নির্দেশ দেওয়া হলে সে গোসল করলো। ফলে সে সর্দিজ্বরে আক্রান্ত হয়ে মারা গেলো। এ সংবাদ নবী (صلى الله عليه وسلم)-এর কাছে পৌঁছলে তিনি বলেন, তারা তাকে হত্যা করেছে, আল্লাহ তাদের হত্যা করুন। অজ্ঞতার প্রতিষেধক কি জিজ্ঞেস নয়? আতা (রাঃ) বলেন, আমাদের নিকট এ সংবাদ পৌঁছেছে যে রসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, সে যদি তার শরীর ধুয়ে নিত এবং তার মাথা যেখানে আঘাত পেয়েছিল তা বাদ দিত! আতা তার নিকট পৌঁছেছে এ কথা ব্যতীত হাসান।</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1627</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَلِيُّ بْنُ مُحَمَّدٍ حَدَّثَنَا أَبُو مُعَاوِيَةَ عَنْ عَبْدِ الرَّحْمَنِ بْنِ أَبِي بَكْرٍ عَنْ ابْنِ أَبِي مُلَيْكَةَ عَنْ عَائِشَةَ قَالَتْ لَمَّا قُبِضَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم وَأَبُو بَكْرٍ عِنْدَ امْرَأَتِهِ ابْنَةِ خَارِجَةَ بِالْعَوَالِي فَجَعَلُوا يَقُولُونَ لَمْ يَمُتْ النَّبِيُّ صلى الله عليه وسلم إِنَّمَا هُوَ بَعْضُ مَا كَانَ يَأْخُذُهُ عِنْدَ الْوَحْيِ فَجَاءَ أَبُو بَكْرٍ فَكَشَفَ عَنْ وَجْهِهِ وَقَبَّلَ بَيْنَ عَيْنَيْهِ وَقَالَ «أَنْتَ أَكْرَمُ عَلَى اللهِ مِنْ أَنْ يُمِيتَكَ مَرَّتَيْنِ قَدْ وَاللهِ مَاتَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم وَعُمَرُ فِي نَاحِيَةِ الْمَسْجِدِ يَقُولُ وَاللهِ مَا مَاتَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم وَلَا يَمُوتُ حَتَّى يَقْطَعَ أَيْدِيَ أُنَاسٍ مِنْ الْمُنَافِقِينَ كَثِيرٍ وَأَرْجُلَهُمْ فَقَامَ أَبُو بَكْرٍ فَصَعِدَ الْمِنْبَرَ فَقَالَ مَنْ كَانَ يَعْبُدُ اللهَ فَإِنَّ اللهَ حَيٌّ لَمْ يَمُتْ وَمَنْ كَانَ يَعْبُدُ مُحَمَّدًا فَإِنَّ مُحَمَّدًا قَدْ مَاتَ {وَمَا مُحَمَّدٌ إِلَّا رَسُولٌ قَدْ خَلَتْ مِنْ قَبْلِهِ الرُّسُلُ أَفَإِنْ مَاتَ أَوْ قُتِلَ انْقَلَبْتُمْ عَلَى أَعْقَابِكُمْ وَمَنْ يَنْقَلِبْ عَلَى عَقِبَيْهِ فَلَنْ يَضُرَّ اللهَ شَيْئًا وَسَيَجْزِي اللهُ الشَّاكِرِينَ}» قَالَ عُمَرُ فَلَكَأَنِّي لَمْ أَقْرَأْهَا إِلَّا يَوْمَئِذٍ.</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, যখন রসূলুল্লাহ (صلى الله عليه وسلم) ইনতিকাল করেন তখন আবু বকর (রাঃ) আওয়ালী নামক স্থানে তার স্ত্রী বিনতে খারিজার ঘরে ছিলেন। লোকজন বলতে লাগলো, নবী (صلى الله عليه وسلم) ইনতিকাল করেননি, বরং ওহী নাযিলের সময় তার যে অবস্থা হতো, এটা তাই। ইতোমধ্যে আবু বকর (রাঃ) এসে তার মুখমণ্ডল থেকে কাপড় সরিয়ে তার দুই চোখের মাঝখানে চুমু দিয়ে বলেন, আপনি দ্বিতীয়বার মারা যাবেন না। আপনি আল্লাহর কাছে অধিক সম্মানিত। আল্লাহর শপথ! রসূলুল্লাহ (صلى الله عليه وسلم) অবশ্যই ইনতিকাল করেছেন। উমর (রাঃ) তখন মসজিদের এক কোণ থেকে বলছিলেন, আল্লাহর শপথ! রসূলুল্লাহ (صلى الله عليه وسلم) ইনতিকাল করেন নি। আর তিনি ব্যাপকভাবে মুনাফিকদের শক্তি খর্ব না করা পর্যন্ত ইনতিকাল করবেন না। তখন আবু বকর (রাঃ) মিম্বারে উঠে দাঁড়িয়ে বলেন, যে ব্যক্তি আল্লাহর ইবাদত করতো সে যেন মনে রাখে, আল্লাহ চিরঞ্জীব, তিনি কখনও মরবেন না। আর যে ব্যক্তি মুহাম্মদের ইবাদত করতো সে জেনে রাখুক, মুহাম্মদ তো ইনতিকাল করেছেন। "মুহাম্মদ একজন রসূল মাত্র, তার পূর্বে অনেক রসূল গত হয়েছে। সুতরাং যদি সে মারা যায় অথবা সে শহীদ হয়, তবে কি তোমরা পৃষ্ঠ প্রদর্শন করবে? কেউ পৃষ্ঠ প্রদর্শন করলে সে কখনও আল্লাহর ক্ষতি করতে পারবে না, বরং আল্লাহ অচিরেই কৃতজ্ঞদের পুরস্কৃত করবেন" (সূরা আল ইমরান: ১৪৪)। উমর (রাঃ) বলেন, আমার মনে হলো, আমি যেন এ আয়াত আজই পড়ছি।</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>3753</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا هِشَامُ بْنُ عَمَّارٍ، حَدَّثَنَا الْهِقْلُ بْنُ زِيَادٍ، حَدَّثَنَا الأَوْزَاعِيُّ، عَنْ عَبْدِ اللَّهِ بْنِ عَامِرٍ الأَسْلَمِيِّ، عَنْ عَمْرِو بْنِ شُعَيْبٍ، عَنْ أَبِيهِ، عَنْ جَدِّهِ، أَنَّ رَسُولَ اللَّهِ ـ صلى الله عليه وسلم ـ قَالَ ‏ "‏ لاَ يَقُصُّ عَلَى النَّاسِ إِلاَّ أَمِيرٌ أَوْ مَأْمُورٌ أَوْ مُرَاءٍ ‏"‏ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেন: শাসক অথবা তার অধীনস্থ কর্মচারী অথবা ফেরেববাজরাই মানুষের মধ্যে কিচ্ছা-কাহিনী বলে বেড়ায়।</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>3754</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَلِيُّ بْنُ مُحَمَّدٍ، حَدَّثَنَا وَكِيعٌ، عَنِ الْعُمَرِيِّ، عَنْ نَافِعٍ، عَنِ ابْنِ عُمَرَ، قَالَ لَمْ يَكُنِ الْقَصَصُ فِي زَمَنِ رَسُولِ اللَّهِ ـ صلى الله عليه وسلم ـ وَلاَ زَمَنِ أَبِي بَكْرٍ وَلاَ زَمَنِ عُمَرَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (صلى الله عليه وسلم)-এর যুগে এবং আবু বকর ও উমর (রাঃ)-এর যুগে কিস্‌সা-কাহিনী বর্ণনার প্রচলন ছিল না।</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
